--- a/economy-premises-and-conditions-to-invest-in-the-stock-market/gcdi.xlsx
+++ b/economy-premises-and-conditions-to-invest-in-the-stock-market/gcdi.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\scott\Documents\Me\Download\new\analysis\economy-premises-and-conditions-to-invest-in-the-stock-market\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C09D3485-4D13-4C90-AF58-4E0C3DCA2F70}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE3F309F-1E62-4F5D-9234-D33B174D53EA}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="9000" windowHeight="13340" xr2:uid="{0C80CCEF-97DA-4DE0-82F5-57ADF1CB0594}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="GCDI.BA" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$H$245</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">GCDI.BA!$A$1:$H$245</definedName>
   </definedNames>
   <calcPr calcId="179021"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>-</t>
   </si>
@@ -62,7 +62,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
@@ -235,7 +235,7 @@
   <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="2" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -250,43 +250,43 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="2" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="14" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="14" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="15" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="15" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="16" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="16" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="17" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="17" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>

--- a/economy-premises-and-conditions-to-invest-in-the-stock-market/gcdi.xlsx
+++ b/economy-premises-and-conditions-to-invest-in-the-stock-market/gcdi.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\scott\Documents\Me\Download\new\analysis\economy-premises-and-conditions-to-invest-in-the-stock-market\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE3F309F-1E62-4F5D-9234-D33B174D53EA}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9B56424-E80A-4EB5-92CE-DF4CC74EEFB2}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="9000" windowHeight="13340" xr2:uid="{0C80CCEF-97DA-4DE0-82F5-57ADF1CB0594}"/>
   </bookViews>
@@ -76,28 +76,28 @@
       <b/>
       <sz val="8"/>
       <color theme="3" tint="0.79998168889431442"/>
-      <name val="Nirmala UI"/>
+      <name val="Segoe UI Historic"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="8"/>
       <color theme="2"/>
-      <name val="Nirmala UI"/>
+      <name val="Segoe UI Historic"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="8"/>
       <color theme="1" tint="0.14996795556505021"/>
-      <name val="Nirmala UI"/>
+      <name val="Segoe UI Historic"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="8"/>
       <color theme="1" tint="0.14999847407452621"/>
-      <name val="Nirmala UI"/>
+      <name val="Segoe UI Historic"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -234,60 +234,68 @@
   </cellStyleXfs>
   <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
     <xf numFmtId="164" fontId="2" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="2" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
     <xf numFmtId="2" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
     <xf numFmtId="164" fontId="2" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="164" fontId="1" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="164" fontId="1" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="164" fontId="1" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="164" fontId="1" fillId="14" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="164" fontId="1" fillId="15" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="164" fontId="1" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="17" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="164" fontId="1" fillId="16" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="17" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -611,17 +619,17 @@
   <dimension ref="A1:H244"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="8.453125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.1796875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.90625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.81640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.26953125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.54296875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.54296875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11" customWidth="1"/>
+    <col min="2" max="2" width="8.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.453125" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="11.26953125" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="8.36328125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.08984375" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="9.90625" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -647,7 +655,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2">
         <v>46128</v>
       </c>
@@ -674,7 +682,7 @@
         <v>Up</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="2">
         <v>46127</v>
       </c>
@@ -701,7 +709,7 @@
         <v>Up</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="2">
         <v>46126</v>
       </c>
@@ -728,7 +736,7 @@
         <v>Down</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="2">
         <v>46125</v>
       </c>
@@ -755,7 +763,7 @@
         <v>Up</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="2">
         <v>46122</v>
       </c>
@@ -782,7 +790,7 @@
         <v>Down</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="2">
         <v>46121</v>
       </c>
@@ -809,7 +817,7 @@
         <v>Up</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="2">
         <v>46120</v>
       </c>
@@ -836,7 +844,7 @@
         <v>Down</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="2">
         <v>46119</v>
       </c>
@@ -863,7 +871,7 @@
         <v>Down</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="2">
         <v>46118</v>
       </c>
@@ -890,7 +898,7 @@
         <v>Same</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="2">
         <v>46113</v>
       </c>
@@ -917,7 +925,7 @@
         <v>Up</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="9">
         <v>46112</v>
       </c>
@@ -944,7 +952,7 @@
         <v>Up</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="9">
         <v>46111</v>
       </c>
@@ -971,7 +979,7 @@
         <v>Up</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="9">
         <v>46108</v>
       </c>
@@ -998,7 +1006,7 @@
         <v>Down</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="9">
         <v>46107</v>
       </c>
@@ -1025,7 +1033,7 @@
         <v>Down</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="9">
         <v>46106</v>
       </c>
@@ -1052,7 +1060,7 @@
         <v>Up</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="9">
         <v>46104</v>
       </c>
@@ -1079,7 +1087,7 @@
         <v>Up</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="9">
         <v>46101</v>
       </c>
@@ -1106,7 +1114,7 @@
         <v>Down</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="9">
         <v>46100</v>
       </c>
@@ -1133,7 +1141,7 @@
         <v>Up</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="9">
         <v>46099</v>
       </c>
@@ -1160,7 +1168,7 @@
         <v>Up</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="9">
         <v>46098</v>
       </c>
@@ -1187,7 +1195,7 @@
         <v>Down</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="9">
         <v>46097</v>
       </c>
@@ -1214,7 +1222,7 @@
         <v>Down</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="9">
         <v>46094</v>
       </c>
@@ -1241,7 +1249,7 @@
         <v>Down</v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="9">
         <v>46093</v>
       </c>
@@ -1268,7 +1276,7 @@
         <v>Down</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="9">
         <v>46092</v>
       </c>
@@ -1295,7 +1303,7 @@
         <v>Up</v>
       </c>
     </row>
-    <row r="26" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="9">
         <v>46091</v>
       </c>
@@ -1322,7 +1330,7 @@
         <v>Up</v>
       </c>
     </row>
-    <row r="27" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="9">
         <v>46090</v>
       </c>
@@ -1349,7 +1357,7 @@
         <v>Up</v>
       </c>
     </row>
-    <row r="28" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="9">
         <v>46087</v>
       </c>
@@ -1376,7 +1384,7 @@
         <v>Same</v>
       </c>
     </row>
-    <row r="29" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="9">
         <v>46086</v>
       </c>
@@ -1403,7 +1411,7 @@
         <v>Up</v>
       </c>
     </row>
-    <row r="30" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="9">
         <v>46085</v>
       </c>
@@ -1430,7 +1438,7 @@
         <v>Up</v>
       </c>
     </row>
-    <row r="31" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="9">
         <v>46084</v>
       </c>
@@ -1457,7 +1465,7 @@
         <v>Down</v>
       </c>
     </row>
-    <row r="32" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="9">
         <v>46083</v>
       </c>
@@ -1484,7 +1492,7 @@
         <v>Up</v>
       </c>
     </row>
-    <row r="33" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="10">
         <v>46080</v>
       </c>
@@ -1511,7 +1519,7 @@
         <v>Up</v>
       </c>
     </row>
-    <row r="34" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="10">
         <v>46079</v>
       </c>
@@ -1538,7 +1546,7 @@
         <v>Same</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="10">
         <v>46078</v>
       </c>
@@ -1565,7 +1573,7 @@
         <v>Down</v>
       </c>
     </row>
-    <row r="36" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="10">
         <v>46077</v>
       </c>
@@ -1592,7 +1600,7 @@
         <v>Down</v>
       </c>
     </row>
-    <row r="37" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="10">
         <v>46076</v>
       </c>
@@ -1619,7 +1627,7 @@
         <v>Down</v>
       </c>
     </row>
-    <row r="38" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="10">
         <v>46073</v>
       </c>
@@ -1646,7 +1654,7 @@
         <v>Down</v>
       </c>
     </row>
-    <row r="39" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="10">
         <v>46072</v>
       </c>
@@ -1673,7 +1681,7 @@
         <v>Same</v>
       </c>
     </row>
-    <row r="40" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="10">
         <v>46071</v>
       </c>
@@ -1700,7 +1708,7 @@
         <v>Down</v>
       </c>
     </row>
-    <row r="41" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="10">
         <v>46066</v>
       </c>
@@ -1727,7 +1735,7 @@
         <v>Down</v>
       </c>
     </row>
-    <row r="42" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="10">
         <v>46065</v>
       </c>
@@ -1754,7 +1762,7 @@
         <v>Down</v>
       </c>
     </row>
-    <row r="43" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="10">
         <v>46064</v>
       </c>
@@ -1781,7 +1789,7 @@
         <v>Up</v>
       </c>
     </row>
-    <row r="44" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="10">
         <v>46063</v>
       </c>
@@ -1808,7 +1816,7 @@
         <v>Down</v>
       </c>
     </row>
-    <row r="45" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="10">
         <v>46062</v>
       </c>
@@ -1835,7 +1843,7 @@
         <v>Up</v>
       </c>
     </row>
-    <row r="46" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="10">
         <v>46059</v>
       </c>
@@ -1862,7 +1870,7 @@
         <v>Down</v>
       </c>
     </row>
-    <row r="47" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="10">
         <v>46058</v>
       </c>
@@ -1889,7 +1897,7 @@
         <v>Down</v>
       </c>
     </row>
-    <row r="48" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="10">
         <v>46057</v>
       </c>
@@ -1916,7 +1924,7 @@
         <v>Down</v>
       </c>
     </row>
-    <row r="49" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="10">
         <v>46056</v>
       </c>
@@ -1943,7 +1951,7 @@
         <v>Down</v>
       </c>
     </row>
-    <row r="50" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="10">
         <v>46055</v>
       </c>
@@ -1970,7 +1978,7 @@
         <v>Down</v>
       </c>
     </row>
-    <row r="51" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="11">
         <v>46052</v>
       </c>
@@ -1997,7 +2005,7 @@
         <v>Up</v>
       </c>
     </row>
-    <row r="52" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="11">
         <v>46051</v>
       </c>
@@ -2024,7 +2032,7 @@
         <v>Down</v>
       </c>
     </row>
-    <row r="53" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53" s="11">
         <v>46050</v>
       </c>
@@ -2051,7 +2059,7 @@
         <v>Same</v>
       </c>
     </row>
-    <row r="54" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="11">
         <v>46049</v>
       </c>
@@ -2078,7 +2086,7 @@
         <v>Down</v>
       </c>
     </row>
-    <row r="55" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A55" s="11">
         <v>46048</v>
       </c>
@@ -2105,7 +2113,7 @@
         <v>Same</v>
       </c>
     </row>
-    <row r="56" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56" s="11">
         <v>46045</v>
       </c>
@@ -2132,7 +2140,7 @@
         <v>Same</v>
       </c>
     </row>
-    <row r="57" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A57" s="11">
         <v>46044</v>
       </c>
@@ -2159,7 +2167,7 @@
         <v>Up</v>
       </c>
     </row>
-    <row r="58" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A58" s="11">
         <v>46043</v>
       </c>
@@ -2186,7 +2194,7 @@
         <v>Down</v>
       </c>
     </row>
-    <row r="59" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A59" s="11">
         <v>46042</v>
       </c>
@@ -2213,7 +2221,7 @@
         <v>Down</v>
       </c>
     </row>
-    <row r="60" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A60" s="11">
         <v>46041</v>
       </c>
@@ -2240,7 +2248,7 @@
         <v>Up</v>
       </c>
     </row>
-    <row r="61" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A61" s="11">
         <v>46038</v>
       </c>
@@ -2267,7 +2275,7 @@
         <v>Down</v>
       </c>
     </row>
-    <row r="62" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A62" s="11">
         <v>46037</v>
       </c>
@@ -2294,7 +2302,7 @@
         <v>Down</v>
       </c>
     </row>
-    <row r="63" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="11">
         <v>46036</v>
       </c>
@@ -2321,7 +2329,7 @@
         <v>Down</v>
       </c>
     </row>
-    <row r="64" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A64" s="11">
         <v>46035</v>
       </c>
@@ -2348,7 +2356,7 @@
         <v>Up</v>
       </c>
     </row>
-    <row r="65" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A65" s="11">
         <v>46034</v>
       </c>
@@ -2375,7 +2383,7 @@
         <v>Same</v>
       </c>
     </row>
-    <row r="66" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A66" s="11">
         <v>46031</v>
       </c>
@@ -2402,7 +2410,7 @@
         <v>Up</v>
       </c>
     </row>
-    <row r="67" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A67" s="11">
         <v>46030</v>
       </c>
@@ -2429,7 +2437,7 @@
         <v>Down</v>
       </c>
     </row>
-    <row r="68" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A68" s="11">
         <v>46029</v>
       </c>
@@ -2456,7 +2464,7 @@
         <v>Same</v>
       </c>
     </row>
-    <row r="69" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A69" s="11">
         <v>46028</v>
       </c>
@@ -2483,7 +2491,7 @@
         <v>Down</v>
       </c>
     </row>
-    <row r="70" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A70" s="11">
         <v>46027</v>
       </c>
@@ -2510,7 +2518,7 @@
         <v>Down</v>
       </c>
     </row>
-    <row r="71" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A71" s="11">
         <v>46024</v>
       </c>
@@ -2537,7 +2545,7 @@
         <v>Up</v>
       </c>
     </row>
-    <row r="72" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A72" s="12">
         <v>46021</v>
       </c>
@@ -2564,7 +2572,7 @@
         <v>Down</v>
       </c>
     </row>
-    <row r="73" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A73" s="12">
         <v>46020</v>
       </c>
@@ -2591,7 +2599,7 @@
         <v>Down</v>
       </c>
     </row>
-    <row r="74" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A74" s="12">
         <v>46017</v>
       </c>
@@ -2618,7 +2626,7 @@
         <v>Down</v>
       </c>
     </row>
-    <row r="75" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A75" s="12">
         <v>46015</v>
       </c>
@@ -2645,7 +2653,7 @@
         <v>Same</v>
       </c>
     </row>
-    <row r="76" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A76" s="12">
         <v>46014</v>
       </c>
@@ -2672,7 +2680,7 @@
         <v>Down</v>
       </c>
     </row>
-    <row r="77" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A77" s="12">
         <v>46013</v>
       </c>
@@ -2699,7 +2707,7 @@
         <v>Up</v>
       </c>
     </row>
-    <row r="78" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A78" s="12">
         <v>46010</v>
       </c>
@@ -2726,7 +2734,7 @@
         <v>Up</v>
       </c>
     </row>
-    <row r="79" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A79" s="12">
         <v>46009</v>
       </c>
@@ -2753,7 +2761,7 @@
         <v>Up</v>
       </c>
     </row>
-    <row r="80" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A80" s="12">
         <v>46008</v>
       </c>
@@ -2780,7 +2788,7 @@
         <v>Up</v>
       </c>
     </row>
-    <row r="81" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A81" s="12">
         <v>46007</v>
       </c>
@@ -2807,7 +2815,7 @@
         <v>Up</v>
       </c>
     </row>
-    <row r="82" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A82" s="12">
         <v>46006</v>
       </c>
@@ -2834,7 +2842,7 @@
         <v>Down</v>
       </c>
     </row>
-    <row r="83" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A83" s="12">
         <v>46003</v>
       </c>
@@ -2861,7 +2869,7 @@
         <v>Down</v>
       </c>
     </row>
-    <row r="84" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A84" s="12">
         <v>46002</v>
       </c>
@@ -2888,7 +2896,7 @@
         <v>Down</v>
       </c>
     </row>
-    <row r="85" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A85" s="12">
         <v>46001</v>
       </c>
@@ -2915,7 +2923,7 @@
         <v>Down</v>
       </c>
     </row>
-    <row r="86" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A86" s="12">
         <v>46000</v>
       </c>
@@ -2942,7 +2950,7 @@
         <v>Down</v>
       </c>
     </row>
-    <row r="87" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A87" s="12">
         <v>45996</v>
       </c>
@@ -2969,7 +2977,7 @@
         <v>Up</v>
       </c>
     </row>
-    <row r="88" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A88" s="12">
         <v>45995</v>
       </c>
@@ -2996,7 +3004,7 @@
         <v>Up</v>
       </c>
     </row>
-    <row r="89" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A89" s="12">
         <v>45994</v>
       </c>
@@ -3023,7 +3031,7 @@
         <v>Down</v>
       </c>
     </row>
-    <row r="90" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A90" s="12">
         <v>45993</v>
       </c>
@@ -3050,7 +3058,7 @@
         <v>Up</v>
       </c>
     </row>
-    <row r="91" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A91" s="12">
         <v>45992</v>
       </c>
@@ -3077,7 +3085,7 @@
         <v>Down</v>
       </c>
     </row>
-    <row r="92" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A92" s="14">
         <v>45989</v>
       </c>
@@ -3104,7 +3112,7 @@
         <v>Same</v>
       </c>
     </row>
-    <row r="93" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A93" s="14">
         <v>45988</v>
       </c>
@@ -3131,7 +3139,7 @@
         <v>Up</v>
       </c>
     </row>
-    <row r="94" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A94" s="14">
         <v>45987</v>
       </c>
@@ -3158,7 +3166,7 @@
         <v>Up</v>
       </c>
     </row>
-    <row r="95" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A95" s="14">
         <v>45986</v>
       </c>
@@ -3185,7 +3193,7 @@
         <v>Down</v>
       </c>
     </row>
-    <row r="96" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A96" s="14">
         <v>45982</v>
       </c>
@@ -3212,7 +3220,7 @@
         <v>Down</v>
       </c>
     </row>
-    <row r="97" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A97" s="14">
         <v>45981</v>
       </c>
@@ -3239,7 +3247,7 @@
         <v>Down</v>
       </c>
     </row>
-    <row r="98" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A98" s="14">
         <v>45980</v>
       </c>
@@ -3266,7 +3274,7 @@
         <v>Up</v>
       </c>
     </row>
-    <row r="99" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A99" s="14">
         <v>45979</v>
       </c>
@@ -3293,7 +3301,7 @@
         <v>Down</v>
       </c>
     </row>
-    <row r="100" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A100" s="14">
         <v>45978</v>
       </c>
@@ -3320,7 +3328,7 @@
         <v>Up</v>
       </c>
     </row>
-    <row r="101" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A101" s="14">
         <v>45975</v>
       </c>
@@ -3347,7 +3355,7 @@
         <v>Up</v>
       </c>
     </row>
-    <row r="102" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A102" s="14">
         <v>45974</v>
       </c>
@@ -3374,7 +3382,7 @@
         <v>Down</v>
       </c>
     </row>
-    <row r="103" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A103" s="14">
         <v>45973</v>
       </c>
@@ -3401,7 +3409,7 @@
         <v>Up</v>
       </c>
     </row>
-    <row r="104" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A104" s="14">
         <v>45972</v>
       </c>
@@ -3428,7 +3436,7 @@
         <v>Up</v>
       </c>
     </row>
-    <row r="105" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A105" s="14">
         <v>45971</v>
       </c>
@@ -3455,7 +3463,7 @@
         <v>Up</v>
       </c>
     </row>
-    <row r="106" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A106" s="14">
         <v>45968</v>
       </c>
@@ -3482,7 +3490,7 @@
         <v>Down</v>
       </c>
     </row>
-    <row r="107" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A107" s="14">
         <v>45967</v>
       </c>
@@ -3509,7 +3517,7 @@
         <v>Down</v>
       </c>
     </row>
-    <row r="108" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A108" s="14">
         <v>45966</v>
       </c>
@@ -3536,7 +3544,7 @@
         <v>Up</v>
       </c>
     </row>
-    <row r="109" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A109" s="14">
         <v>45965</v>
       </c>
@@ -3563,7 +3571,7 @@
         <v>Down</v>
       </c>
     </row>
-    <row r="110" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A110" s="14">
         <v>45964</v>
       </c>
@@ -3590,7 +3598,7 @@
         <v>Up</v>
       </c>
     </row>
-    <row r="111" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A111" s="15">
         <v>45961</v>
       </c>
@@ -3617,7 +3625,7 @@
         <v>Up</v>
       </c>
     </row>
-    <row r="112" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A112" s="15">
         <v>45960</v>
       </c>
@@ -3644,7 +3652,7 @@
         <v>Up</v>
       </c>
     </row>
-    <row r="113" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A113" s="15">
         <v>45959</v>
       </c>
@@ -3671,7 +3679,7 @@
         <v>Up</v>
       </c>
     </row>
-    <row r="114" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A114" s="15">
         <v>45958</v>
       </c>
@@ -3698,7 +3706,7 @@
         <v>Up</v>
       </c>
     </row>
-    <row r="115" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A115" s="15">
         <v>45957</v>
       </c>
@@ -3725,7 +3733,7 @@
         <v>Up</v>
       </c>
     </row>
-    <row r="116" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A116" s="15">
         <v>45954</v>
       </c>
@@ -3752,7 +3760,7 @@
         <v>Down</v>
       </c>
     </row>
-    <row r="117" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A117" s="15">
         <v>45953</v>
       </c>
@@ -3779,7 +3787,7 @@
         <v>Up</v>
       </c>
     </row>
-    <row r="118" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A118" s="15">
         <v>45952</v>
       </c>
@@ -3806,7 +3814,7 @@
         <v>Down</v>
       </c>
     </row>
-    <row r="119" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A119" s="15">
         <v>45951</v>
       </c>
@@ -3833,7 +3841,7 @@
         <v>Up</v>
       </c>
     </row>
-    <row r="120" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A120" s="15">
         <v>45950</v>
       </c>
@@ -3860,7 +3868,7 @@
         <v>Down</v>
       </c>
     </row>
-    <row r="121" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A121" s="15">
         <v>45947</v>
       </c>
@@ -3887,7 +3895,7 @@
         <v>Down</v>
       </c>
     </row>
-    <row r="122" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A122" s="15">
         <v>45946</v>
       </c>
@@ -3914,7 +3922,7 @@
         <v>Down</v>
       </c>
     </row>
-    <row r="123" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A123" s="15">
         <v>45945</v>
       </c>
@@ -3941,7 +3949,7 @@
         <v>Up</v>
       </c>
     </row>
-    <row r="124" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A124" s="15">
         <v>45944</v>
       </c>
@@ -3968,7 +3976,7 @@
         <v>Down</v>
       </c>
     </row>
-    <row r="125" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A125" s="15">
         <v>45943</v>
       </c>
@@ -3995,7 +4003,7 @@
         <v>Up</v>
       </c>
     </row>
-    <row r="126" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A126" s="15">
         <v>45939</v>
       </c>
@@ -4022,7 +4030,7 @@
         <v>Up</v>
       </c>
     </row>
-    <row r="127" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A127" s="15">
         <v>45938</v>
       </c>
@@ -4049,7 +4057,7 @@
         <v>Up</v>
       </c>
     </row>
-    <row r="128" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A128" s="15">
         <v>45937</v>
       </c>
@@ -4076,7 +4084,7 @@
         <v>Up</v>
       </c>
     </row>
-    <row r="129" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A129" s="15">
         <v>45936</v>
       </c>
@@ -4103,7 +4111,7 @@
         <v>Down</v>
       </c>
     </row>
-    <row r="130" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A130" s="15">
         <v>45933</v>
       </c>
@@ -4130,7 +4138,7 @@
         <v>Down</v>
       </c>
     </row>
-    <row r="131" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A131" s="15">
         <v>45932</v>
       </c>
@@ -4157,7 +4165,7 @@
         <v>Up</v>
       </c>
     </row>
-    <row r="132" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A132" s="15">
         <v>45931</v>
       </c>
@@ -4184,7 +4192,7 @@
         <v>Down</v>
       </c>
     </row>
-    <row r="133" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A133" s="16">
         <v>45930</v>
       </c>
@@ -4211,7 +4219,7 @@
         <v>Down</v>
       </c>
     </row>
-    <row r="134" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A134" s="16">
         <v>45929</v>
       </c>
@@ -4238,7 +4246,7 @@
         <v>Up</v>
       </c>
     </row>
-    <row r="135" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A135" s="16">
         <v>45926</v>
       </c>
@@ -4265,7 +4273,7 @@
         <v>Down</v>
       </c>
     </row>
-    <row r="136" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A136" s="16">
         <v>45925</v>
       </c>
@@ -4292,7 +4300,7 @@
         <v>Down</v>
       </c>
     </row>
-    <row r="137" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A137" s="16">
         <v>45924</v>
       </c>
@@ -4319,7 +4327,7 @@
         <v>Up</v>
       </c>
     </row>
-    <row r="138" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A138" s="16">
         <v>45923</v>
       </c>
@@ -4346,7 +4354,7 @@
         <v>Up</v>
       </c>
     </row>
-    <row r="139" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A139" s="16">
         <v>45922</v>
       </c>
@@ -4373,7 +4381,7 @@
         <v>Up</v>
       </c>
     </row>
-    <row r="140" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A140" s="16">
         <v>45919</v>
       </c>
@@ -4400,7 +4408,7 @@
         <v>Same</v>
       </c>
     </row>
-    <row r="141" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A141" s="16">
         <v>45918</v>
       </c>
@@ -4427,7 +4435,7 @@
         <v>Down</v>
       </c>
     </row>
-    <row r="142" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A142" s="16">
         <v>45917</v>
       </c>
@@ -4454,7 +4462,7 @@
         <v>Down</v>
       </c>
     </row>
-    <row r="143" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A143" s="16">
         <v>45916</v>
       </c>
@@ -4481,7 +4489,7 @@
         <v>Down</v>
       </c>
     </row>
-    <row r="144" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A144" s="16">
         <v>45915</v>
       </c>
@@ -4508,7 +4516,7 @@
         <v>Down</v>
       </c>
     </row>
-    <row r="145" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A145" s="16">
         <v>45912</v>
       </c>
@@ -4535,7 +4543,7 @@
         <v>Down</v>
       </c>
     </row>
-    <row r="146" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A146" s="16">
         <v>45911</v>
       </c>
@@ -4562,7 +4570,7 @@
         <v>Up</v>
       </c>
     </row>
-    <row r="147" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A147" s="16">
         <v>45910</v>
       </c>
@@ -4589,7 +4597,7 @@
         <v>Up</v>
       </c>
     </row>
-    <row r="148" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A148" s="16">
         <v>45909</v>
       </c>
@@ -4616,7 +4624,7 @@
         <v>Up</v>
       </c>
     </row>
-    <row r="149" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A149" s="16">
         <v>45908</v>
       </c>
@@ -4643,7 +4651,7 @@
         <v>Down</v>
       </c>
     </row>
-    <row r="150" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A150" s="16">
         <v>45905</v>
       </c>
@@ -4670,7 +4678,7 @@
         <v>Down</v>
       </c>
     </row>
-    <row r="151" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A151" s="16">
         <v>45904</v>
       </c>
@@ -4697,7 +4705,7 @@
         <v>Up</v>
       </c>
     </row>
-    <row r="152" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A152" s="16">
         <v>45903</v>
       </c>
@@ -4724,7 +4732,7 @@
         <v>Same</v>
       </c>
     </row>
-    <row r="153" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A153" s="16">
         <v>45902</v>
       </c>
@@ -4751,7 +4759,7 @@
         <v>Down</v>
       </c>
     </row>
-    <row r="154" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A154" s="16">
         <v>45901</v>
       </c>
@@ -4778,7 +4786,7 @@
         <v>Down</v>
       </c>
     </row>
-    <row r="155" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A155" s="17">
         <v>45898</v>
       </c>
@@ -4805,7 +4813,7 @@
         <v>Up</v>
       </c>
     </row>
-    <row r="156" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A156" s="17">
         <v>45897</v>
       </c>
@@ -4832,7 +4840,7 @@
         <v>Up</v>
       </c>
     </row>
-    <row r="157" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A157" s="17">
         <v>45896</v>
       </c>
@@ -4859,7 +4867,7 @@
         <v>Down</v>
       </c>
     </row>
-    <row r="158" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A158" s="17">
         <v>45895</v>
       </c>
@@ -4886,7 +4894,7 @@
         <v>Same</v>
       </c>
     </row>
-    <row r="159" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A159" s="17">
         <v>45894</v>
       </c>
@@ -4913,7 +4921,7 @@
         <v>Down</v>
       </c>
     </row>
-    <row r="160" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A160" s="17">
         <v>45891</v>
       </c>
@@ -4940,7 +4948,7 @@
         <v>Up</v>
       </c>
     </row>
-    <row r="161" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A161" s="17">
         <v>45890</v>
       </c>
@@ -4967,7 +4975,7 @@
         <v>Down</v>
       </c>
     </row>
-    <row r="162" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A162" s="17">
         <v>45889</v>
       </c>
@@ -4994,7 +5002,7 @@
         <v>Up</v>
       </c>
     </row>
-    <row r="163" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A163" s="17">
         <v>45888</v>
       </c>
@@ -5021,7 +5029,7 @@
         <v>Down</v>
       </c>
     </row>
-    <row r="164" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A164" s="17">
         <v>45887</v>
       </c>
@@ -5048,7 +5056,7 @@
         <v>Up</v>
       </c>
     </row>
-    <row r="165" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A165" s="17">
         <v>45883</v>
       </c>
@@ -5075,7 +5083,7 @@
         <v>Down</v>
       </c>
     </row>
-    <row r="166" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A166" s="17">
         <v>45882</v>
       </c>
@@ -5102,7 +5110,7 @@
         <v>Up</v>
       </c>
     </row>
-    <row r="167" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A167" s="17">
         <v>45881</v>
       </c>
@@ -5129,7 +5137,7 @@
         <v>Down</v>
       </c>
     </row>
-    <row r="168" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A168" s="17">
         <v>45880</v>
       </c>
@@ -5156,7 +5164,7 @@
         <v>Down</v>
       </c>
     </row>
-    <row r="169" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A169" s="17">
         <v>45877</v>
       </c>
@@ -5183,7 +5191,7 @@
         <v>Same</v>
       </c>
     </row>
-    <row r="170" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A170" s="17">
         <v>45876</v>
       </c>
@@ -5210,7 +5218,7 @@
         <v>Down</v>
       </c>
     </row>
-    <row r="171" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A171" s="17">
         <v>45875</v>
       </c>
@@ -5237,7 +5245,7 @@
         <v>Up</v>
       </c>
     </row>
-    <row r="172" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A172" s="17">
         <v>45874</v>
       </c>
@@ -5264,7 +5272,7 @@
         <v>Down</v>
       </c>
     </row>
-    <row r="173" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A173" s="17">
         <v>45873</v>
       </c>
@@ -5291,7 +5299,7 @@
         <v>Up</v>
       </c>
     </row>
-    <row r="174" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A174" s="17">
         <v>45870</v>
       </c>
@@ -5318,7 +5326,7 @@
         <v>Up</v>
       </c>
     </row>
-    <row r="175" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A175" s="18">
         <v>45869</v>
       </c>
@@ -5345,7 +5353,7 @@
         <v>Up</v>
       </c>
     </row>
-    <row r="176" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A176" s="18">
         <v>45868</v>
       </c>
@@ -5372,7 +5380,7 @@
         <v>Down</v>
       </c>
     </row>
-    <row r="177" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A177" s="18">
         <v>45867</v>
       </c>
@@ -5399,7 +5407,7 @@
         <v>Up</v>
       </c>
     </row>
-    <row r="178" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A178" s="18">
         <v>45866</v>
       </c>
@@ -5426,7 +5434,7 @@
         <v>Up</v>
       </c>
     </row>
-    <row r="179" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A179" s="18">
         <v>45863</v>
       </c>
@@ -5453,7 +5461,7 @@
         <v>Up</v>
       </c>
     </row>
-    <row r="180" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A180" s="18">
         <v>45862</v>
       </c>
@@ -5480,7 +5488,7 @@
         <v>Same</v>
       </c>
     </row>
-    <row r="181" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A181" s="18">
         <v>45861</v>
       </c>
@@ -5507,7 +5515,7 @@
         <v>Up</v>
       </c>
     </row>
-    <row r="182" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A182" s="18">
         <v>45860</v>
       </c>
@@ -5534,7 +5542,7 @@
         <v>Down</v>
       </c>
     </row>
-    <row r="183" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A183" s="18">
         <v>45859</v>
       </c>
@@ -5561,7 +5569,7 @@
         <v>Down</v>
       </c>
     </row>
-    <row r="184" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A184" s="18">
         <v>45856</v>
       </c>
@@ -5588,7 +5596,7 @@
         <v>Up</v>
       </c>
     </row>
-    <row r="185" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A185" s="18">
         <v>45855</v>
       </c>
@@ -5615,7 +5623,7 @@
         <v>Up</v>
       </c>
     </row>
-    <row r="186" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A186" s="18">
         <v>45854</v>
       </c>
@@ -5642,7 +5650,7 @@
         <v>Down</v>
       </c>
     </row>
-    <row r="187" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A187" s="18">
         <v>45853</v>
       </c>
@@ -5669,7 +5677,7 @@
         <v>Down</v>
       </c>
     </row>
-    <row r="188" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A188" s="18">
         <v>45852</v>
       </c>
@@ -5696,7 +5704,7 @@
         <v>Up</v>
       </c>
     </row>
-    <row r="189" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A189" s="18">
         <v>45849</v>
       </c>
@@ -5723,7 +5731,7 @@
         <v>Down</v>
       </c>
     </row>
-    <row r="190" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A190" s="18">
         <v>45848</v>
       </c>
@@ -5750,7 +5758,7 @@
         <v>Down</v>
       </c>
     </row>
-    <row r="191" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A191" s="18">
         <v>45846</v>
       </c>
@@ -5777,7 +5785,7 @@
         <v>Same</v>
       </c>
     </row>
-    <row r="192" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A192" s="18">
         <v>45845</v>
       </c>
@@ -5804,7 +5812,7 @@
         <v>Down</v>
       </c>
     </row>
-    <row r="193" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A193" s="18">
         <v>45842</v>
       </c>
@@ -5831,7 +5839,7 @@
         <v>Down</v>
       </c>
     </row>
-    <row r="194" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A194" s="18">
         <v>45841</v>
       </c>
@@ -5858,7 +5866,7 @@
         <v>Same</v>
       </c>
     </row>
-    <row r="195" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A195" s="18">
         <v>45840</v>
       </c>
@@ -5885,7 +5893,7 @@
         <v>Up</v>
       </c>
     </row>
-    <row r="196" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A196" s="18">
         <v>45839</v>
       </c>
@@ -5912,7 +5920,7 @@
         <v>Up</v>
       </c>
     </row>
-    <row r="197" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A197" s="19">
         <v>45838</v>
       </c>
@@ -5939,7 +5947,7 @@
         <v>Down</v>
       </c>
     </row>
-    <row r="198" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A198" s="19">
         <v>45835</v>
       </c>
@@ -5966,7 +5974,7 @@
         <v>Down</v>
       </c>
     </row>
-    <row r="199" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A199" s="19">
         <v>45834</v>
       </c>
@@ -5993,7 +6001,7 @@
         <v>Up</v>
       </c>
     </row>
-    <row r="200" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A200" s="19">
         <v>45833</v>
       </c>
@@ -6020,7 +6028,7 @@
         <v>Same</v>
       </c>
     </row>
-    <row r="201" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A201" s="19">
         <v>45832</v>
       </c>
@@ -6047,7 +6055,7 @@
         <v>Up</v>
       </c>
     </row>
-    <row r="202" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A202" s="19">
         <v>45831</v>
       </c>
@@ -6074,7 +6082,7 @@
         <v>Down</v>
       </c>
     </row>
-    <row r="203" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A203" s="19">
         <v>45827</v>
       </c>
@@ -6101,7 +6109,7 @@
         <v>Down</v>
       </c>
     </row>
-    <row r="204" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A204" s="19">
         <v>45826</v>
       </c>
@@ -6128,7 +6136,7 @@
         <v>Down</v>
       </c>
     </row>
-    <row r="205" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A205" s="19">
         <v>45825</v>
       </c>
@@ -6155,7 +6163,7 @@
         <v>Down</v>
       </c>
     </row>
-    <row r="206" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A206" s="19">
         <v>45821</v>
       </c>
@@ -6182,7 +6190,7 @@
         <v>Down</v>
       </c>
     </row>
-    <row r="207" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A207" s="19">
         <v>45820</v>
       </c>
@@ -6209,7 +6217,7 @@
         <v>Up</v>
       </c>
     </row>
-    <row r="208" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A208" s="19">
         <v>45819</v>
       </c>
@@ -6236,7 +6244,7 @@
         <v>Down</v>
       </c>
     </row>
-    <row r="209" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A209" s="19">
         <v>45818</v>
       </c>
@@ -6263,7 +6271,7 @@
         <v>Up</v>
       </c>
     </row>
-    <row r="210" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A210" s="19">
         <v>45817</v>
       </c>
@@ -6290,7 +6298,7 @@
         <v>Down</v>
       </c>
     </row>
-    <row r="211" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A211" s="19">
         <v>45814</v>
       </c>
@@ -6317,7 +6325,7 @@
         <v>Down</v>
       </c>
     </row>
-    <row r="212" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A212" s="19">
         <v>45813</v>
       </c>
@@ -6344,7 +6352,7 @@
         <v>Down</v>
       </c>
     </row>
-    <row r="213" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A213" s="19">
         <v>45812</v>
       </c>
@@ -6371,7 +6379,7 @@
         <v>Down</v>
       </c>
     </row>
-    <row r="214" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A214" s="19">
         <v>45811</v>
       </c>
@@ -6398,7 +6406,7 @@
         <v>Down</v>
       </c>
     </row>
-    <row r="215" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A215" s="19">
         <v>45810</v>
       </c>
@@ -6425,8 +6433,8 @@
         <v>Down</v>
       </c>
     </row>
-    <row r="216" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A216" s="21">
+    <row r="216" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A216" s="20">
         <v>45807</v>
       </c>
       <c r="B216" s="3">
@@ -6452,8 +6460,8 @@
         <v>Up</v>
       </c>
     </row>
-    <row r="217" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A217" s="21">
+    <row r="217" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A217" s="20">
         <v>45806</v>
       </c>
       <c r="B217" s="3">
@@ -6479,8 +6487,8 @@
         <v>Down</v>
       </c>
     </row>
-    <row r="218" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A218" s="21">
+    <row r="218" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A218" s="20">
         <v>45805</v>
       </c>
       <c r="B218" s="3">
@@ -6506,8 +6514,8 @@
         <v>Down</v>
       </c>
     </row>
-    <row r="219" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A219" s="21">
+    <row r="219" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A219" s="20">
         <v>45804</v>
       </c>
       <c r="B219" s="3">
@@ -6533,8 +6541,8 @@
         <v>Down</v>
       </c>
     </row>
-    <row r="220" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A220" s="21">
+    <row r="220" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A220" s="20">
         <v>45803</v>
       </c>
       <c r="B220" s="3">
@@ -6560,8 +6568,8 @@
         <v>Down</v>
       </c>
     </row>
-    <row r="221" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A221" s="21">
+    <row r="221" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A221" s="20">
         <v>45800</v>
       </c>
       <c r="B221" s="3">
@@ -6587,8 +6595,8 @@
         <v>Up</v>
       </c>
     </row>
-    <row r="222" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A222" s="21">
+    <row r="222" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A222" s="20">
         <v>45799</v>
       </c>
       <c r="B222" s="3">
@@ -6614,8 +6622,8 @@
         <v>Down</v>
       </c>
     </row>
-    <row r="223" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A223" s="21">
+    <row r="223" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A223" s="20">
         <v>45798</v>
       </c>
       <c r="B223" s="3">
@@ -6641,8 +6649,8 @@
         <v>Down</v>
       </c>
     </row>
-    <row r="224" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A224" s="21">
+    <row r="224" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A224" s="20">
         <v>45797</v>
       </c>
       <c r="B224" s="3">
@@ -6668,8 +6676,8 @@
         <v>Down</v>
       </c>
     </row>
-    <row r="225" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A225" s="21">
+    <row r="225" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A225" s="20">
         <v>45796</v>
       </c>
       <c r="B225" s="3">
@@ -6695,8 +6703,8 @@
         <v>Down</v>
       </c>
     </row>
-    <row r="226" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A226" s="21">
+    <row r="226" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A226" s="20">
         <v>45793</v>
       </c>
       <c r="B226" s="3">
@@ -6722,8 +6730,8 @@
         <v>Up</v>
       </c>
     </row>
-    <row r="227" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A227" s="21">
+    <row r="227" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A227" s="20">
         <v>45792</v>
       </c>
       <c r="B227" s="3">
@@ -6749,8 +6757,8 @@
         <v>Up</v>
       </c>
     </row>
-    <row r="228" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A228" s="21">
+    <row r="228" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A228" s="20">
         <v>45791</v>
       </c>
       <c r="B228" s="3">
@@ -6776,8 +6784,8 @@
         <v>Up</v>
       </c>
     </row>
-    <row r="229" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A229" s="21">
+    <row r="229" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A229" s="20">
         <v>45790</v>
       </c>
       <c r="B229" s="3">
@@ -6803,8 +6811,8 @@
         <v>Up</v>
       </c>
     </row>
-    <row r="230" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A230" s="21">
+    <row r="230" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A230" s="20">
         <v>45789</v>
       </c>
       <c r="B230" s="3">
@@ -6830,8 +6838,8 @@
         <v>Up</v>
       </c>
     </row>
-    <row r="231" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A231" s="21">
+    <row r="231" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A231" s="20">
         <v>45786</v>
       </c>
       <c r="B231" s="3">
@@ -6857,8 +6865,8 @@
         <v>Down</v>
       </c>
     </row>
-    <row r="232" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A232" s="21">
+    <row r="232" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A232" s="20">
         <v>45785</v>
       </c>
       <c r="B232" s="3">
@@ -6884,8 +6892,8 @@
         <v>Down</v>
       </c>
     </row>
-    <row r="233" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A233" s="21">
+    <row r="233" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A233" s="20">
         <v>45784</v>
       </c>
       <c r="B233" s="3">
@@ -6911,8 +6919,8 @@
         <v>Up</v>
       </c>
     </row>
-    <row r="234" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A234" s="21">
+    <row r="234" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A234" s="20">
         <v>45783</v>
       </c>
       <c r="B234" s="3">
@@ -6938,8 +6946,8 @@
         <v>Up</v>
       </c>
     </row>
-    <row r="235" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A235" s="21">
+    <row r="235" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A235" s="20">
         <v>45782</v>
       </c>
       <c r="B235" s="3">
@@ -6965,8 +6973,8 @@
         <v>Down</v>
       </c>
     </row>
-    <row r="236" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A236" s="20">
+    <row r="236" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A236" s="21">
         <v>45777</v>
       </c>
       <c r="B236" s="3">
@@ -6992,8 +7000,8 @@
         <v>Down</v>
       </c>
     </row>
-    <row r="237" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A237" s="20">
+    <row r="237" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A237" s="21">
         <v>45776</v>
       </c>
       <c r="B237" s="3">
@@ -7019,8 +7027,8 @@
         <v>Down</v>
       </c>
     </row>
-    <row r="238" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A238" s="20">
+    <row r="238" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A238" s="21">
         <v>45775</v>
       </c>
       <c r="B238" s="3">
@@ -7046,8 +7054,8 @@
         <v>Up</v>
       </c>
     </row>
-    <row r="239" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A239" s="20">
+    <row r="239" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A239" s="21">
         <v>45772</v>
       </c>
       <c r="B239" s="3">
@@ -7073,8 +7081,8 @@
         <v>Down</v>
       </c>
     </row>
-    <row r="240" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A240" s="20">
+    <row r="240" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A240" s="21">
         <v>45771</v>
       </c>
       <c r="B240" s="3">
@@ -7100,8 +7108,8 @@
         <v>Same</v>
       </c>
     </row>
-    <row r="241" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A241" s="20">
+    <row r="241" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A241" s="21">
         <v>45770</v>
       </c>
       <c r="B241" s="3">
@@ -7127,8 +7135,8 @@
         <v>Up</v>
       </c>
     </row>
-    <row r="242" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A242" s="20">
+    <row r="242" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A242" s="21">
         <v>45769</v>
       </c>
       <c r="B242" s="3">
@@ -7154,8 +7162,8 @@
         <v>Up</v>
       </c>
     </row>
-    <row r="243" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A243" s="20">
+    <row r="243" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A243" s="21">
         <v>45768</v>
       </c>
       <c r="B243" s="3">
@@ -7181,8 +7189,8 @@
         <v>Down</v>
       </c>
     </row>
-    <row r="244" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A244" s="20">
+    <row r="244" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A244" s="21">
         <v>45763</v>
       </c>
       <c r="B244" s="3">
